--- a/mom/docs/forms/frm-700-maintenance/FRM-722_Product_Identification_Tag.xlsx
+++ b/mom/docs/forms/frm-700-maintenance/FRM-722_Product_Identification_Tag.xlsx
@@ -4957,6 +4957,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Số lượng trong khay
+Số chi tiết thực tế trong khay — đếm và ghi chính xác.</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
+      <text>
+        <t>Lô / số mẻ
+Lô hoặc số heat vật liệu — phục vụ truy xuất.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>Khay xanh dương
+Đánh dấu khi sản phẩm đang gia công hoặc chờ kiểm tra.</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>Khay vàng
+Đánh dấu khi hàng lỗi đang chờ xác nhận / chờ sửa.</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>Khay đỏ
+Đánh dấu khi hàng NG — phải đưa về khu cách ly NG.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5281,7 +5321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BS40"/>
+  <dimension ref="A2:AN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5959,7 +5999,7 @@
     <row r="16" ht="17" customHeight="1" s="264">
       <c r="A16" s="470" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  TRAY STATUS (mark one per WI-703)</t>
+          <t xml:space="preserve">  2.  TRAY STATUS — MARK ONE (per WI-703)</t>
         </is>
       </c>
       <c r="B16" s="471" t="n"/>
@@ -6005,7 +6045,7 @@
     <row r="17" ht="20" customHeight="1" s="264">
       <c r="A17" s="473" t="inlineStr">
         <is>
-          <t>Tray Status Selected</t>
+          <t>XANH DƯƠNG — Đang gia công / Chờ kiểm tra</t>
         </is>
       </c>
       <c r="B17" s="474" t="n"/>
@@ -6029,7 +6069,7 @@
       <c r="T17" s="475" t="n"/>
       <c r="U17" s="477" t="inlineStr">
         <is>
-          <t>XANH DƯƠNG — Đang gia công / Chờ kiểm tra</t>
+          <t>Tình trạng: sản phẩm trong quá trình sản xuất</t>
         </is>
       </c>
       <c r="V17" s="474" t="n"/>
@@ -6055,7 +6095,7 @@
     <row r="18" ht="20" customHeight="1" s="264">
       <c r="A18" s="480" t="inlineStr">
         <is>
-          <t>Status Confirmed By</t>
+          <t>VÀNG — Hàng lỗi / Chờ xác nhận / Chờ sửa</t>
         </is>
       </c>
       <c r="B18" s="481" t="n"/>
@@ -6079,7 +6119,7 @@
       <c r="T18" s="482" t="n"/>
       <c r="U18" s="484" t="inlineStr">
         <is>
-          <t>VÀNG — Hàng lỗi / Chờ xác nhận / Chờ sửa</t>
+          <t>Tình trạng: chờ QC xác nhận hoặc chờ sửa</t>
         </is>
       </c>
       <c r="V18" s="481" t="n"/>
@@ -6105,7 +6145,7 @@
     <row r="19" ht="20" customHeight="1" s="264">
       <c r="A19" s="487" t="inlineStr">
         <is>
-          <t>Status Change Date</t>
+          <t>ĐỎ — Hàng không phù hợp (NG) — Cách ly</t>
         </is>
       </c>
       <c r="B19" s="488" t="n"/>
@@ -6129,7 +6169,7 @@
       <c r="T19" s="489" t="n"/>
       <c r="U19" s="491" t="inlineStr">
         <is>
-          <t>ĐỎ — Hàng không phù hợp (NG) — Cách ly</t>
+          <t>Tình trạng: hàng NG, để khu cách ly</t>
         </is>
       </c>
       <c r="V19" s="488" t="n"/>
@@ -7060,7 +7100,7 @@
     <row r="40" ht="24" customHeight="1" s="264">
       <c r="A40" s="515" t="inlineStr">
         <is>
-          <t>NOTICE — One tag accompanies every tray. Tag colour status must always match the physical tray colour (WI-703). Update the tag and tray immediately when product status changes. Ref: WI-703. Retain: with lot.</t>
+          <t>NOTICE — One tag accompanies every tray. The tag colour status must always match the physical tray colour (WI-703). Update the tag and tray immediately when product status changes. Ref: WI-703. Retain: with the lot. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
         </is>
       </c>
       <c r="B40" s="471" t="n"/>
@@ -7225,6 +7265,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
